--- a/5/search/combined_defense_results/best_strategy_summary.xlsx
+++ b/5/search/combined_defense_results/best_strategy_summary.xlsx
@@ -452,16 +452,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>23.66000000000069</v>
+        <v>20.88000000000024</v>
       </c>
       <c r="B2" t="n">
-        <v>9.470000000000478</v>
+        <v>9.48000000000048</v>
       </c>
       <c r="C2" t="n">
-        <v>7.569999999999839</v>
+        <v>7.649999999999837</v>
       </c>
       <c r="D2" t="n">
-        <v>6.620000000000365</v>
+        <v>3.749999999999922</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/combined_defense_results/best_strategy_summary.xlsx
+++ b/5/search/combined_defense_results/best_strategy_summary.xlsx
@@ -425,26 +425,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>combined_score</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>total_time</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>balance_factor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>M1_time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>M2_time</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>M3_time</t>
         </is>
@@ -452,16 +462,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20.88000000000024</v>
+        <v>36.65874650841936</v>
       </c>
       <c r="B2" t="n">
-        <v>9.48000000000048</v>
+        <v>20.84000000000024</v>
       </c>
       <c r="C2" t="n">
-        <v>7.649999999999837</v>
+        <v>0.9317615569752826</v>
       </c>
       <c r="D2" t="n">
-        <v>3.749999999999922</v>
+        <v>6.41</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7.629999999999837</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6.800000000000399</v>
       </c>
     </row>
   </sheetData>
